--- a/resultados/Swift_completos_exp.xlsx
+++ b/resultados/Swift_completos_exp.xlsx
@@ -2,11 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="26745" yWindow="3210" windowWidth="19800" windowHeight="10695" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet name="V1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="V2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="181029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -42,7 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -462,7 +467,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Receiver</t>
+          <t>Sender</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -565,7 +570,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>4113</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>novomode-s-a-citius33xxx-a1cebde7</t>
@@ -626,7 +635,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4137</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>importadora-maduro-sa-chasus33xxx-1c4a5e63</t>
@@ -687,7 +700,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>5038</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>piamonte-sa-bofaus3nxxx-68485396</t>
@@ -748,7 +765,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>5039</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>novomode-s-a-citius33xxx-a1cebde7</t>
@@ -809,7 +830,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>5085</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>distribuidora-textil-del-ecuador-di-citius33xxx-36f5d77d</t>
@@ -870,7 +895,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>5086</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>comodin-sa-chasus33xxx-cf197890</t>
@@ -931,7 +960,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>blanca-carolina-valencia-molina-bofaus3mxxx-fb62f4bc</t>
@@ -992,7 +1025,9 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>5130</v>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>importadora-maduro-sa-pnbpus3nnyc-25d8e8ab</t>
@@ -1053,7 +1088,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>5131</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>blanca-carolina-valencia-molina-bofaus3mxxx-fb62f4bc</t>
@@ -1114,7 +1153,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>5137</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>novomode-s-a-citius33xxx-a1cebde7</t>
@@ -1175,7 +1218,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>5178</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>importadora-maduro-sa-pnbpus3nnyc-25d8e8ab</t>
@@ -1236,7 +1283,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>5182</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>piamonte-sa-citius33xxx-a51a5041</t>
@@ -1297,7 +1348,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>5181</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>piamonte-sa-citius33xxx-a51a5041</t>
@@ -1358,7 +1413,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>5222</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>fashion-trademarks-holding-sl-citius33xxx-632d180e</t>
@@ -1419,7 +1478,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>6001</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>novomode-s-a-citius33xxx-a1cebde7</t>
@@ -1480,7 +1543,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>6002</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>novomode-s-a-citius33xxx-a1cebde7</t>
@@ -1541,7 +1608,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>6053</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>distribuidora-textil-del-ecuador-di-citius33xxx-36f5d77d</t>
@@ -1602,7 +1673,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>6056</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>krokom-sac-citius33xxx-4d8d8fbd</t>
@@ -1663,7 +1738,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>6055</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>novomode-s-a-citius33xxx-a1cebde7</t>
@@ -1724,7 +1803,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>6195</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>balnor-bv-chasus33xxx-e76d67f4</t>
@@ -1785,7 +1868,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>7001</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>comodin-sa-chasus33xxx-cf197890</t>
@@ -1846,7 +1933,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>7053</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>novomode-s-a-citius33xxx-a1cebde7</t>
@@ -1907,7 +1998,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>7098</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>importadora-maduro-sa-bofaus3mxxx-a24ee335</t>
@@ -1968,7 +2063,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>7134</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>distribuidora-textil-del-ecuador-di-citius33xxx-36f5d77d</t>
@@ -2029,7 +2128,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>piamonte-sa-bofaus3nxxx-68485396</t>
@@ -2090,7 +2193,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>piamonte-sa-bofaus3nxxx-68485396</t>
@@ -2151,7 +2258,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>8020</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>novomode-s-a-citius33xxx-a1cebde7</t>
@@ -2212,7 +2323,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>8019</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>novomode-s-a-citius33xxx-a1cebde7</t>
@@ -2273,7 +2388,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>8041</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>distribuidora-textil-del-ecuador-di-citius33xxx-36f5d77d</t>
@@ -2334,7 +2453,9 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>8045</v>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>piamonte-sa-citius33xxx-a51a5041</t>
@@ -2395,7 +2516,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>8045</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>piamonte-sa-citius33xxx-a51a5041</t>
@@ -2456,7 +2581,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>8047</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>blanca-carolina-valencia-molina-bofaus3mxxx-fb62f4bc</t>
@@ -2517,7 +2646,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>8066</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>comodin-sas-pnbpus3nnyc-fbd346cc</t>
@@ -2578,7 +2711,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>8073</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>blanca-carolina-valencia-molina-bofaus3mxxx-fb62f4bc</t>
@@ -2639,7 +2776,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>8072</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>comodin-sas-pnbpus3nnyc-fbd346cc</t>
@@ -2700,7 +2841,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>8134</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>importadora-maduro-sa-chasus33xxx-1c4a5e63</t>
@@ -2761,7 +2906,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>9027</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>novomode-s-a-citius33xxx-a1cebde7</t>
@@ -2822,7 +2971,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>9028</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>novomode-s-a-citius33xxx-a1cebde7</t>
@@ -2883,7 +3036,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>9031</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>comodin-sas-pnbpus3nnyc-fbd346cc</t>
@@ -2944,7 +3101,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>9032</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>importadora-maduro-sa-chasus33xxx-1c4a5e63</t>
@@ -3005,7 +3166,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>9026</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>novomode-s-a-citius33xxx-a1cebde7</t>
@@ -3066,7 +3231,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>fu-sheng-nv-pnbpus3nnyc-93f8afa3</t>
@@ -3127,7 +3296,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>9063</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>novomode-s-a-citius33xxx-a1cebde7</t>
@@ -3188,7 +3361,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>piamonte-sa-bofaus3nxxx-68485396</t>
@@ -3249,7 +3426,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>9092</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>piamonte-sa-bofaus3nxxx-68485396</t>
@@ -3310,7 +3491,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>9093</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>blanca-carolina-valencia-molina-bofaus3mxxx-fb62f4bc</t>
@@ -3371,7 +3556,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>9090</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>balnor-bv-chasus33xxx-e76d67f4</t>
@@ -3432,7 +3621,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>9125</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>krokom-sac-citius33xxx-4d8d8fbd</t>
@@ -3493,7 +3686,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>10044</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>novomode-s-a-citius33xxx-a1cebde7</t>
@@ -3554,7 +3751,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>10043</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>novomode-s-a-citius33xxx-a1cebde7</t>
@@ -3615,7 +3816,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>10184</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>distribuidora-textil-del-ecuador-di-citius33xxx-36f5d77d</t>
@@ -3676,7 +3881,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>10185</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>distribuidora-textil-del-ecuador-di-citius33xxx-36f5d77d</t>
@@ -3737,7 +3946,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>10183</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>distribuidora-textil-del-ecuado-citius33xxx-7eec573e</t>
@@ -3798,7 +4011,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>10071</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>importadora-maduro-sa-chasus33xxx-1c4a5e63</t>
@@ -3859,7 +4076,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>10076</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>saga-falabella-sa-chasus33xxx-b4d77158</t>
@@ -3920,7 +4141,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>10074</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>krokom-sac-citius33xxx-4d8d8fbd</t>
@@ -3981,7 +4206,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>10113</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>novomode-s-a-citius33xxx-a1cebde7</t>
@@ -4015,7 +4244,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>14273</v>
+        <v>14273.8</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4042,7 +4271,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>10172</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>importadora-maduro-sa-citius33xxx-16f222d9</t>
@@ -4103,7 +4336,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>10146</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>comodin-sas-pnbpus3nnyc-fbd346cc</t>
@@ -4164,7 +4401,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>11022</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>importadora-maduro-sa-chasus33xxx-1c4a5e63</t>
@@ -4225,7 +4466,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>11030</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>fu-sheng-nv-pnbpus3nnyc-93f8afa3</t>
@@ -4286,7 +4531,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>11032</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>novomode-s-a-citius33xxx-a1cebde7</t>
@@ -4347,7 +4596,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>11031</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>novomode-s-a-citius33xxx-a1cebde7</t>
@@ -4408,7 +4661,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>11058</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>distribuidora-textil-del-ecuador-di-citius33xxx-36f5d77d</t>
@@ -4469,7 +4726,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>4002</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>mercadeo-y-moda-sa-agrogtgcxxx-25a7737a</t>
@@ -4530,7 +4791,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>4001</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>balnor-bv-chasus33xxx-e76d67f4</t>
@@ -4591,7 +4856,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>4033</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>importadora-maduro-sa-chasus33xxx-1c4a5e63</t>
@@ -4652,7 +4921,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>4032</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>manufacturas-interamericana-sa-citius33xxx-5fb2194d</t>
@@ -4713,7 +4986,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>4052</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>distribuidora-textil-del-ecuador-di-citius33xxx-36f5d77d</t>
@@ -4774,7 +5051,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>4055</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>distribuidora-textil-del-ecuador-di-citius33xxx-36f5d77d</t>
@@ -4835,7 +5116,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>4093</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>comodin-sa-nw-47326473</t>
@@ -4896,7 +5181,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>4112</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>saga-falabella-sa-chasus33xxx-f2aa0d71</t>
@@ -4957,7 +5246,9 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="n">
+        <v>5034</v>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>importadora-maduro-sa-chasus33xxx-1c4a5e63</t>
@@ -5018,7 +5309,9 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="n">
+        <v>5037</v>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>piamonte-sa-bofaus3nxxx-68485396</t>
@@ -5079,7 +5372,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>5040</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>saga-falabella-sa-chasus33xxx-f2aa0d71</t>
@@ -5140,7 +5437,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>5084</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>distribuidora-textil-del-ecuador-di-citius33xxx-36f5d77d</t>
@@ -5201,7 +5502,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>5092-5592</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>krokom-sac-citius33xxx-4d8d8fbd</t>
@@ -5262,7 +5567,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>5136</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>manufacturas-interamericana-sa-citius33xxx-5fb2194d</t>
@@ -5323,7 +5632,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>5180</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>comodin-sa-nw-47326473</t>
@@ -5384,7 +5697,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>6003</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>krokom-sac-citius33xxx-4d8d8fbd</t>
@@ -5445,7 +5762,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>6054</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>distribuidora-textil-del-ecuador-di-citius33xxx-36f5d77d</t>
@@ -5506,7 +5827,9 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="n">
+        <v>6093</v>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>blanca-carolina-valencia-molina-bofaus3mxxx-fb62f4bc</t>
@@ -5567,7 +5890,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>6094</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>importadora-maduro-sa-citius33xxx-16f222d9</t>
@@ -5628,7 +5955,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>6194</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>saga-falabella-sa-chasus33xxx-f2aa0d71</t>
@@ -5689,7 +6020,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>importadora-maduro-sa-chasus33xxx-1c4a5e63</t>
@@ -5750,7 +6085,9 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="n">
+        <v>7002</v>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>piamonte-sa-citius33xxx-a51a5041</t>
@@ -5811,7 +6148,9 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="n">
+        <v>7003</v>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>piamonte-sa-citius33xxx-a51a5041</t>
@@ -6116,7 +6455,9 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="n">
+        <v>7101</v>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>blanca-carolina-valencia-molina-bofaus3mxxx-fb62f4bc</t>
@@ -6177,7 +6518,9 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="n">
+        <v>7135</v>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>blanca-carolina-valencia-molina-bofaus3mxxx-fb62f4bc</t>
@@ -6238,7 +6581,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>7173</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>saga-falabella-sa-chasus33xxx-f2aa0d71</t>
@@ -6299,7 +6646,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>8018</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>importadora-maduro-sa-pnbpus3nnyc-25d8e8ab</t>
@@ -6360,7 +6711,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>8021</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>blanca-carolina-valencia-molina-bofaus3mxxx-fb62f4bc</t>
@@ -6421,7 +6776,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>8042</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>distribuidora-textil-del-ecuador-di-citius33xxx-36f5d77d</t>
@@ -6482,7 +6841,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>9034</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>distribuidora-textil-del-ecuador-di-citius33xxx-36f5d77d</t>
@@ -6543,7 +6906,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>9033</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>distribuidora-textil-del-ecuador-di-citius33xxx-36f5d77d</t>
@@ -6604,7 +6971,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>9062</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>importadora-maduro-sa-citius33xxx-16f222d9</t>
@@ -6665,7 +7036,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>9094</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>comodin-sa-nw-47326473</t>
@@ -6726,7 +7101,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>9127</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>saga-falabella-sa-chasus33xxx-f2aa0d71</t>
@@ -6787,7 +7166,9 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="n">
+        <v>10027</v>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>importadora-maduro-sa-bofaus3mxxx-a24ee335</t>
@@ -6848,7 +7229,9 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="n">
+        <v>10045</v>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>blanca-carolina-valencia-molina-bofaus3mxxx-fb62f4bc</t>
@@ -6909,7 +7292,9 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="n">
+        <v>10138</v>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>blanca-carolina-valencia-molina-bofaus3mxxx-fb62f4bc</t>
@@ -6970,7 +7355,9 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="n">
+        <v>11003</v>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>piamonte-sa-citius33xxx-a51a5041</t>
@@ -7031,7 +7418,9 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="n">
+        <v>11002</v>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>piamonte-sa-citius33xxx-a51a5041</t>
@@ -7092,7 +7481,9 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="n">
+        <v>11054</v>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>blanca-carolina-valencia-molina-bofaus3mxxx-fb62f4bc</t>
@@ -7295,7 +7686,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>11118</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>saga-falabella-sa-chasus33xxx-b4d77158</t>
@@ -7417,7 +7812,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>12001</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>piamonte-sa-citius33xxx-a51a5041</t>
@@ -7478,7 +7877,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>12002-12902</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>piamonte-sa-citius33xxx-a51a5041</t>
@@ -7539,7 +7942,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>12013</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>piamonte-sa-citius33xxx-a51a5041</t>
@@ -7600,7 +8007,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>12014</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>piamonte-sa-citius33xxx-a51a5041</t>
@@ -7661,7 +8072,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>12066</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>balnor-bv-chasus33xxx-e76d67f4</t>
@@ -7722,7 +8137,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>12067</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>importadora-maduro-sa-pnbpus3nnyc-25d8e8ab</t>
@@ -7844,7 +8263,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>12070</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>importadora-maduro-sa-pnbpus3nnyc-25d8e8ab</t>
@@ -7907,7 +8330,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>12077-12078</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -7970,7 +8393,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>12077-12078</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>distribuidora-textil-del-ecuador-d-citius33xxx-812a9fc7</t>
@@ -8031,7 +8458,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>12079</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>novomode-s-a-citius33xxx-a1cebde7</t>
@@ -8092,7 +8523,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>12080</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>novomode-s-a-citius33xxx-a1cebde7</t>
@@ -8153,7 +8588,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>12082</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>importadora-maduro-sa-citius33xxx-16f222d9</t>
@@ -8214,7 +8653,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>12109</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>novomode-s-a-citius33xxx-a1cebde7</t>
@@ -8275,7 +8718,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>12110</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>novomode-s-a-citius33xxx-a1cebde7</t>
@@ -8336,7 +8783,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>12111</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>novomode-s-a-citius33xxx-a1cebde7</t>
@@ -8397,7 +8848,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>12112</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>comodin-sas-pnbpus3nnyc-fbd346cc</t>

--- a/resultados/Swift_completos_exp.xlsx
+++ b/resultados/Swift_completos_exp.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="26745" yWindow="3210" windowWidth="19800" windowHeight="10695" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="345" yWindow="3210" windowWidth="19800" windowHeight="10695" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="V1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="V2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="181029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -46,8 +46,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
